--- a/tableau/nna_tableau_data.xlsx
+++ b/tableau/nna_tableau_data.xlsx
@@ -3342,7 +3342,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4 quarters found; methods: reported,derived</t>
+          <t>4 quarters found; methods: derived,reported</t>
         </is>
       </c>
     </row>
